--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="184">
   <si>
     <t>Result</t>
   </si>
@@ -620,6 +620,9 @@
   </si>
   <si>
     <t>Mon Nov 03 22:50:54 IST 2025</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 21:38:33 IST 2025</t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1203,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="208">
   <si>
     <t>Result</t>
   </si>
@@ -623,6 +623,78 @@
   </si>
   <si>
     <t>Mon Dec 15 21:38:33 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 19 20:06:24 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 19 22:27:23 IST 2025</t>
+  </si>
+  <si>
+    <t>Thu Dec 25 17:39:56 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:16:02 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:21:31 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:24:10 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:26:33 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:29:19 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:29:51 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:30:30 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:31:13 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:33:49 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:36:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:39:05 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:41:44 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 19:44:29 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:05:01 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:14:36 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:23:49 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:24:37 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:25:32 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:26:20 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:27:10 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Dec 26 20:27:57 IST 2025</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1129,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1085,7 +1157,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1111,7 +1183,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1203,7 +1275,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1290,7 +1362,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>205</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1428,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1532,7 +1604,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1605,7 +1677,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1678,7 +1750,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>207</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1826,7 +1898,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1961,7 +2033,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2035,7 +2107,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2063,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2089,7 +2161,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2157,7 +2229,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2185,7 +2257,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2211,7 +2283,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2276,10 +2348,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2352,7 +2424,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2428,7 +2500,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="210">
   <si>
     <t>Result</t>
   </si>
@@ -695,6 +695,12 @@
   </si>
   <si>
     <t>Fri Dec 26 20:27:57 IST 2025</t>
+  </si>
+  <si>
+    <t>Fri Jan 09 16:59:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 09 17:00:56 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2348,10 +2354,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="232">
   <si>
     <t>Result</t>
   </si>
@@ -701,6 +701,72 @@
   </si>
   <si>
     <t>Fri Jan 09 17:00:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 00:56:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:02:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:05:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:08:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:10:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:11:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:12:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:12:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:20:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:28:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:36:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:38:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 01:41:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:19:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:28:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:37:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:38:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:39:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:39:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:40:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 02:41:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 10 21:23:37 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1132,10 +1198,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1160,10 +1226,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1186,10 +1252,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1281,7 +1347,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1368,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1506,7 +1572,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1610,7 +1676,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1683,7 +1749,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1756,7 +1822,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1904,7 +1970,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2039,7 +2105,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2113,7 +2179,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2141,7 +2207,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2167,7 +2233,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2235,7 +2301,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2263,7 +2329,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2289,7 +2355,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2357,7 +2423,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2430,7 +2496,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2506,7 +2572,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="254">
   <si>
     <t>Result</t>
   </si>
@@ -767,6 +767,72 @@
   </si>
   <si>
     <t>Tue Mar 10 21:23:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:05:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:11:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:13:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:16:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:18:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:19:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:20:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:20:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:23:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:26:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:28:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:31:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:34:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 10:54:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:03:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:11:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:12:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:12:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:13:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:14:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 11:15:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Jun 02 17:24:29 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1198,10 +1264,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1226,10 +1292,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1252,10 +1318,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1344,10 +1410,10 @@
     </row>
     <row ht="130.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1434,7 +1500,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1572,7 +1638,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1676,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1749,7 +1815,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1822,7 +1888,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1970,7 +2036,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2105,7 +2171,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2179,7 +2245,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2207,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2233,7 +2299,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2301,7 +2367,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2329,7 +2395,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2355,7 +2421,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2423,7 +2489,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2496,7 +2562,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2572,7 +2638,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="257">
   <si>
     <t>Result</t>
   </si>
@@ -833,6 +833,15 @@
   </si>
   <si>
     <t>Tue Jun 02 17:24:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 13:29:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 18:08:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 18:14:49 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1410,10 +1419,10 @@
     </row>
     <row ht="130.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="280">
   <si>
     <t>Result</t>
   </si>
@@ -842,6 +842,75 @@
   </si>
   <si>
     <t>Fri Jun 05 18:14:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 23:17:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 23:22:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:37:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:42:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:45:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:48:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:51:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:51:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:52:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:53:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:56:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 00:59:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:01:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:04:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:07:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:30:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:39:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:54:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:55:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:56:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:57:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:58:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 19 01:58:58 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1345,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1304,7 +1373,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1330,7 +1399,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1422,7 +1491,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1509,7 +1578,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1647,7 +1716,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1751,7 +1820,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1824,7 +1893,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1897,7 +1966,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2045,7 +2114,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2180,7 +2249,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2254,7 +2323,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2282,7 +2351,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2308,7 +2377,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2376,7 +2445,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2404,7 +2473,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2430,7 +2499,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2498,7 +2567,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2571,7 +2640,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2647,7 +2716,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="285">
   <si>
     <t>Result</t>
   </si>
@@ -911,6 +911,21 @@
   </si>
   <si>
     <t>Fri Jun 19 01:58:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:47:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 18:54:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 19:02:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 19:09:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jul 06 23:56:14 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1305,7 +1320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1341,10 +1356,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>266</v>
       </c>
       <c r="C2" s="3"/>
@@ -1369,10 +1384,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>267</v>
       </c>
       <c r="C3" s="3"/>
@@ -1395,10 +1410,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>268</v>
       </c>
       <c r="C4" s="3"/>
@@ -1430,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CFB1CD1-F3B6-43AC-8580-D3EB244DA395}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="17.1796875" collapsed="true"/>
@@ -1487,10 +1502,10 @@
       </c>
     </row>
     <row ht="130.5" r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>259</v>
       </c>
       <c r="C2" s="9"/>
@@ -1536,7 +1551,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A934BCA2-85F5-4C93-BBEE-2C380B06E8FD}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" customWidth="true" width="15.453125" collapsed="true"/>
@@ -1566,18 +1581,18 @@
       <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>277</v>
       </c>
       <c r="C2" s="9"/>
@@ -1590,22 +1605,22 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>57</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -1617,22 +1632,22 @@
       <c r="F3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>58</v>
       </c>
       <c r="D4" s="7" t="s">
@@ -1644,11 +1659,11 @@
       <c r="F4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G4" t="str">
+      <c r="G4" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="0">
         <v>54</v>
       </c>
     </row>
@@ -1670,7 +1685,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B956F6-C214-41E0-9C06-CEBF82C79B1D}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" bestFit="true" customWidth="true" width="14.90625" collapsed="true"/>
@@ -1701,21 +1716,21 @@
       <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>276</v>
       </c>
       <c r="C2" s="9"/>
@@ -1728,25 +1743,25 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>61</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -1758,14 +1773,14 @@
       <c r="F3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G3" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>52</v>
       </c>
     </row>
@@ -1776,7 +1791,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14FA0791-CEBE-4D11-B2A1-F3F80E94D9F6}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="9" max="9" bestFit="true" customWidth="true" width="20.453125" collapsed="true"/>
@@ -1805,22 +1820,22 @@
       <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>275</v>
+      <c r="B2" t="s" s="0">
+        <v>284</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1832,17 +1847,17 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>55</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>63</v>
       </c>
     </row>
@@ -1853,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42D40E85-2D41-457A-88AE-C55FF8092C53}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1878,21 +1893,21 @@
       <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>278</v>
       </c>
       <c r="C2" s="9"/>
@@ -1905,17 +1920,17 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>63</v>
       </c>
     </row>
@@ -1926,7 +1941,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CCD7964-6EA7-47FC-8316-5BB19CD71397}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -1951,21 +1966,21 @@
       <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>279</v>
       </c>
       <c r="C2" s="9"/>
@@ -1978,17 +1993,17 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>53</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>56</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>63</v>
       </c>
     </row>
@@ -1999,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971A235C-1EB8-4FB4-A052-AC25C4AD1D51}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -2024,18 +2039,18 @@
       <c r="G1" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>36</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>58</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -2047,14 +2062,14 @@
       <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="str">
+      <c r="G2" t="str" s="0">
         <f>"Bridges"</f>
         <v>Bridges</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>54</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>56</v>
       </c>
     </row>
@@ -2065,7 +2080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D17964-3C9A-4128-9E79-065C6162AEA0}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="12" max="12" customWidth="true" width="9.81640625" collapsed="true"/>
@@ -2110,10 +2125,10 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>260</v>
       </c>
       <c r="C2" s="3"/>
@@ -2144,10 +2159,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>17</v>
       </c>
       <c r="C3" s="3"/>
@@ -2170,10 +2185,10 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>18</v>
       </c>
       <c r="C4" s="3"/>
@@ -2202,7 +2217,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1F3F653-DA45-4F17-B585-55D2A689218D}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="31.0" collapsed="true"/>
@@ -2245,10 +2260,10 @@
       <c r="L1" s="4"/>
     </row>
     <row ht="145" r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>262</v>
       </c>
       <c r="C2" s="3"/>
@@ -2283,7 +2298,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C63CEF1E-9472-4171-9CD3-FA3B036F7CBF}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2319,10 +2334,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>269</v>
       </c>
       <c r="C2" s="3"/>
@@ -2347,10 +2362,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>270</v>
       </c>
       <c r="C3" s="3"/>
@@ -2373,10 +2388,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>271</v>
       </c>
       <c r="C4" s="3"/>
@@ -2405,7 +2420,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D9BFE-7E90-4AE5-8638-D512C4CC008B}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2441,10 +2456,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>263</v>
       </c>
       <c r="C2" s="3"/>
@@ -2469,10 +2484,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>264</v>
       </c>
       <c r="C3" s="3"/>
@@ -2495,10 +2510,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="0">
         <v>265</v>
       </c>
       <c r="C4" s="3"/>
@@ -2527,7 +2542,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C743C20-9154-41EC-9178-39729EDF45F3}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:10" x14ac:dyDescent="0.35">
@@ -2563,10 +2578,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>272</v>
       </c>
       <c r="C2" s="3"/>
@@ -2597,7 +2612,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2AC4ABD-97C1-4B0A-A78A-1F57EE1A6D5C}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -2636,10 +2651,10 @@
       </c>
     </row>
     <row ht="409.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>273</v>
       </c>
       <c r="C2" s="3"/>
@@ -2673,7 +2688,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A0D7E3-B8FB-4BA8-A147-CA4665BD31FB}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row ht="29" r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -2712,10 +2727,10 @@
       </c>
     </row>
     <row ht="362.5" r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>261</v>
       </c>
       <c r="C2" s="3"/>
@@ -2749,7 +2764,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CB2C77F-A6BC-4072-8D66-A2FB7943F35E}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="11" max="11" customWidth="true" width="20.7265625" collapsed="true"/>

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="320">
   <si>
     <t>Result</t>
   </si>
@@ -926,6 +926,111 @@
   </si>
   <si>
     <t>Mon Jul 06 23:56:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:34:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:39:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:42:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:44:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:46:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:47:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:47:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:48:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:50:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:53:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:56:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 10:59:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:01:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 06 11:22:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:16:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:21:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:23:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:24:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:26:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:27:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:28:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:28:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:31:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:33:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:36:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:39:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 00:41:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 01:01:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:30:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:36:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:37:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:38:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:39:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:39:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 08 19:40:31 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1360,7 +1465,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>266</v>
+        <v>306</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1388,7 +1493,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>267</v>
+        <v>307</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1414,7 +1519,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1506,7 +1611,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>259</v>
+        <v>299</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1590,10 +1695,10 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>277</v>
+        <v>317</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1731,7 +1836,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>276</v>
+        <v>316</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1832,10 +1937,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1905,10 +2010,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>278</v>
+        <v>318</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1978,10 +2083,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>279</v>
+        <v>319</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2129,7 +2234,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2264,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2338,7 +2443,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2366,7 +2471,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2392,7 +2497,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>271</v>
+        <v>311</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2460,7 +2565,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2488,7 +2593,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>264</v>
+        <v>304</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2514,7 +2619,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2579,10 +2684,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>272</v>
+        <v>312</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2655,7 +2760,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>273</v>
+        <v>313</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2731,7 +2836,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">

--- a/KatalonData/ABPTestData/PaymentsCC.xlsx
+++ b/KatalonData/ABPTestData/PaymentsCC.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1254" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="341">
   <si>
     <t>Result</t>
   </si>
@@ -1031,6 +1031,69 @@
   </si>
   <si>
     <t>Sat Aug 08 19:40:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:13:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:17:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:19:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:21:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:23:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:23:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:24:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:24:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:27:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:30:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:32:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:35:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:38:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Aug 14 22:58:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:43:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:49:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:50:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:51:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:51:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:52:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 00:53:13 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1528,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1493,7 +1556,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -1519,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -1611,7 +1674,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1695,10 +1758,10 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1836,7 +1899,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -1940,7 +2003,7 @@
         <v>36</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2010,10 +2073,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s" s="0">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2086,7 +2149,7 @@
         <v>36</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="7" t="s">
@@ -2234,7 +2297,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2369,7 +2432,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2443,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2471,7 +2534,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2497,7 +2560,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2565,7 +2628,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2593,7 +2656,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
@@ -2619,7 +2682,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
@@ -2687,7 +2750,7 @@
         <v>36</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2760,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
@@ -2836,7 +2899,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="7" t="s">
